--- a/storage/templates/Manolete.xlsx
+++ b/storage/templates/Manolete.xlsx
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN107"/>
+  <dimension ref="A1:AN109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="25.05" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="7" min="1" max="1"/>
@@ -5945,103 +5945,159 @@
       </c>
     </row>
     <row r="77" ht="25.05" customHeight="1">
-      <c r="C77" s="15">
-        <f>SUM(C7:C76)</f>
-        <v/>
-      </c>
-      <c r="E77" s="22" t="inlineStr">
+      <c r="A77" s="36" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>CAFE GRANO BLEND PROFONDO/ELEGANTE 1 KG</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="16" t="inlineStr">
+        <is>
+          <t>KILO</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="F77" s="25">
+        <f>C77*E77</f>
+        <v/>
+      </c>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="18" t="n"/>
+      <c r="L77" s="18" t="n"/>
+      <c r="M77" s="18" t="n"/>
+      <c r="N77" s="18" t="n"/>
+      <c r="O77" s="18" t="n"/>
+      <c r="P77" s="18" t="n"/>
+      <c r="Q77" s="18" t="n"/>
+      <c r="R77" s="18" t="n"/>
+      <c r="S77" s="18" t="n"/>
+      <c r="T77" s="18" t="n"/>
+      <c r="U77" s="18" t="n"/>
+      <c r="V77" s="18" t="n"/>
+      <c r="W77" s="18" t="n"/>
+      <c r="X77" s="18" t="n"/>
+      <c r="Y77" s="18" t="n"/>
+      <c r="Z77" s="18" t="n"/>
+      <c r="AA77" s="18" t="n"/>
+      <c r="AB77" s="18" t="n"/>
+      <c r="AC77" s="18" t="n"/>
+      <c r="AD77" s="18" t="n"/>
+      <c r="AE77" s="18" t="n"/>
+      <c r="AF77" s="18" t="n"/>
+      <c r="AG77" s="18" t="n"/>
+      <c r="AH77" s="18" t="n"/>
+      <c r="AI77" s="18" t="n"/>
+      <c r="AJ77" s="18" t="n"/>
+      <c r="AK77" s="18" t="n"/>
+      <c r="AL77" s="19">
+        <f>SUM(G77:AK77)</f>
+        <v/>
+      </c>
+      <c r="AM77" s="20">
+        <f>SUM(C77,AL77)</f>
+        <v/>
+      </c>
+      <c r="AN77" s="21">
+        <f>E77*AM77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="25.05" customHeight="1">
+      <c r="A78" s="36" t="inlineStr">
+        <is>
+          <t>934021</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>VINO BCO NUBORI VERDEJO 75 CL</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F78" s="25">
+        <f>C78*E78</f>
+        <v/>
+      </c>
+      <c r="G78" s="18" t="n"/>
+      <c r="H78" s="18" t="n"/>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="n"/>
+      <c r="L78" s="18" t="n"/>
+      <c r="M78" s="18" t="n"/>
+      <c r="N78" s="18" t="n"/>
+      <c r="O78" s="18" t="n"/>
+      <c r="P78" s="18" t="n"/>
+      <c r="Q78" s="18" t="n"/>
+      <c r="R78" s="18" t="n"/>
+      <c r="S78" s="18" t="n"/>
+      <c r="T78" s="18" t="n"/>
+      <c r="U78" s="18" t="n"/>
+      <c r="V78" s="18" t="n"/>
+      <c r="W78" s="18" t="n"/>
+      <c r="X78" s="18" t="n"/>
+      <c r="Y78" s="18" t="n"/>
+      <c r="Z78" s="18" t="n"/>
+      <c r="AA78" s="18" t="n"/>
+      <c r="AB78" s="18" t="n"/>
+      <c r="AC78" s="18" t="n"/>
+      <c r="AD78" s="18" t="n"/>
+      <c r="AE78" s="18" t="n"/>
+      <c r="AF78" s="18" t="n"/>
+      <c r="AG78" s="18" t="n"/>
+      <c r="AH78" s="18" t="n"/>
+      <c r="AI78" s="18" t="n"/>
+      <c r="AJ78" s="18" t="n"/>
+      <c r="AK78" s="18" t="n"/>
+      <c r="AL78" s="19">
+        <f>SUM(G78:AK78)</f>
+        <v/>
+      </c>
+      <c r="AM78" s="20">
+        <f>SUM(C78,AL78)</f>
+        <v/>
+      </c>
+      <c r="AN78" s="21">
+        <f>E78*AM78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="25.05" customHeight="1">
+      <c r="C79" s="15">
+        <f>SUM(C7:C78)</f>
+        <v/>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F77" s="23">
-        <f>SUM(F7:F76)</f>
-        <v/>
-      </c>
-      <c r="G77" s="14" t="n"/>
-      <c r="H77" s="14" t="n"/>
-      <c r="I77" s="14" t="n"/>
-      <c r="J77" s="14" t="n"/>
-      <c r="K77" s="14" t="n"/>
-      <c r="L77" s="14" t="n"/>
-      <c r="M77" s="14" t="n"/>
-      <c r="N77" s="14" t="n"/>
-      <c r="O77" s="14" t="n"/>
-      <c r="P77" s="14" t="n"/>
-      <c r="Q77" s="14" t="n"/>
-      <c r="R77" s="14" t="n"/>
-      <c r="S77" s="14" t="n"/>
-      <c r="T77" s="14" t="n"/>
-      <c r="U77" s="14" t="n"/>
-      <c r="V77" s="14" t="n"/>
-      <c r="W77" s="14" t="n"/>
-      <c r="X77" s="14" t="n"/>
-      <c r="Y77" s="14" t="n"/>
-      <c r="Z77" s="14" t="n"/>
-      <c r="AA77" s="14" t="n"/>
-      <c r="AB77" s="14" t="n"/>
-      <c r="AC77" s="14" t="n"/>
-      <c r="AD77" s="14" t="n"/>
-      <c r="AE77" s="14" t="n"/>
-      <c r="AF77" s="14" t="n"/>
-      <c r="AG77" s="14" t="n"/>
-      <c r="AH77" s="14" t="n"/>
-      <c r="AI77" s="14" t="n"/>
-      <c r="AJ77" s="14" t="n"/>
-      <c r="AK77" s="14" t="n"/>
-      <c r="AL77" s="14" t="n"/>
-      <c r="AM77" s="14">
-        <f>SUM(AM7:AM76)</f>
-        <v/>
-      </c>
-      <c r="AN77" s="24">
-        <f>SUM(AN7:AN76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="25.05" customHeight="1">
-      <c r="D78" s="14" t="n"/>
-      <c r="E78" s="14" t="n"/>
-      <c r="F78" s="14" t="n"/>
-      <c r="G78" s="14" t="n"/>
-      <c r="H78" s="14" t="n"/>
-      <c r="I78" s="14" t="n"/>
-      <c r="J78" s="14" t="n"/>
-      <c r="K78" s="14" t="n"/>
-      <c r="L78" s="14" t="n"/>
-      <c r="M78" s="14" t="n"/>
-      <c r="N78" s="14" t="n"/>
-      <c r="O78" s="14" t="n"/>
-      <c r="P78" s="14" t="n"/>
-      <c r="Q78" s="14" t="n"/>
-      <c r="R78" s="14" t="n"/>
-      <c r="S78" s="14" t="n"/>
-      <c r="T78" s="14" t="n"/>
-      <c r="U78" s="14" t="n"/>
-      <c r="V78" s="14" t="n"/>
-      <c r="W78" s="14" t="n"/>
-      <c r="X78" s="14" t="n"/>
-      <c r="Y78" s="14" t="n"/>
-      <c r="Z78" s="14" t="n"/>
-      <c r="AA78" s="14" t="n"/>
-      <c r="AB78" s="14" t="n"/>
-      <c r="AC78" s="14" t="n"/>
-      <c r="AD78" s="14" t="n"/>
-      <c r="AE78" s="14" t="n"/>
-      <c r="AF78" s="14" t="n"/>
-      <c r="AG78" s="14" t="n"/>
-      <c r="AH78" s="14" t="n"/>
-      <c r="AI78" s="14" t="n"/>
-      <c r="AJ78" s="14" t="n"/>
-      <c r="AK78" s="14" t="n"/>
-      <c r="AL78" s="14" t="n"/>
-      <c r="AM78" s="14" t="n"/>
-      <c r="AN78" s="14" t="n"/>
-    </row>
-    <row r="79" ht="25.05" customHeight="1">
-      <c r="D79" s="14" t="n"/>
-      <c r="E79" s="14" t="n"/>
-      <c r="F79" s="14" t="n"/>
+      <c r="F79" s="23">
+        <f>SUM(F7:F78)</f>
+        <v/>
+      </c>
       <c r="G79" s="14" t="n"/>
       <c r="H79" s="14" t="n"/>
       <c r="I79" s="14" t="n"/>
@@ -6074,8 +6130,14 @@
       <c r="AJ79" s="14" t="n"/>
       <c r="AK79" s="14" t="n"/>
       <c r="AL79" s="14" t="n"/>
-      <c r="AM79" s="14" t="n"/>
-      <c r="AN79" s="14" t="n"/>
+      <c r="AM79" s="14">
+        <f>SUM(AM7:AM78)</f>
+        <v/>
+      </c>
+      <c r="AN79" s="24">
+        <f>SUM(AN7:AN78)</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="25.05" customHeight="1">
       <c r="D80" s="14" t="n"/>
@@ -7169,6 +7231,84 @@
       <c r="AM107" s="14" t="n"/>
       <c r="AN107" s="14" t="n"/>
     </row>
+    <row r="108">
+      <c r="D108" s="14" t="n"/>
+      <c r="E108" s="14" t="n"/>
+      <c r="F108" s="14" t="n"/>
+      <c r="G108" s="14" t="n"/>
+      <c r="H108" s="14" t="n"/>
+      <c r="I108" s="14" t="n"/>
+      <c r="J108" s="14" t="n"/>
+      <c r="K108" s="14" t="n"/>
+      <c r="L108" s="14" t="n"/>
+      <c r="M108" s="14" t="n"/>
+      <c r="N108" s="14" t="n"/>
+      <c r="O108" s="14" t="n"/>
+      <c r="P108" s="14" t="n"/>
+      <c r="Q108" s="14" t="n"/>
+      <c r="R108" s="14" t="n"/>
+      <c r="S108" s="14" t="n"/>
+      <c r="T108" s="14" t="n"/>
+      <c r="U108" s="14" t="n"/>
+      <c r="V108" s="14" t="n"/>
+      <c r="W108" s="14" t="n"/>
+      <c r="X108" s="14" t="n"/>
+      <c r="Y108" s="14" t="n"/>
+      <c r="Z108" s="14" t="n"/>
+      <c r="AA108" s="14" t="n"/>
+      <c r="AB108" s="14" t="n"/>
+      <c r="AC108" s="14" t="n"/>
+      <c r="AD108" s="14" t="n"/>
+      <c r="AE108" s="14" t="n"/>
+      <c r="AF108" s="14" t="n"/>
+      <c r="AG108" s="14" t="n"/>
+      <c r="AH108" s="14" t="n"/>
+      <c r="AI108" s="14" t="n"/>
+      <c r="AJ108" s="14" t="n"/>
+      <c r="AK108" s="14" t="n"/>
+      <c r="AL108" s="14" t="n"/>
+      <c r="AM108" s="14" t="n"/>
+      <c r="AN108" s="14" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="14" t="n"/>
+      <c r="E109" s="14" t="n"/>
+      <c r="F109" s="14" t="n"/>
+      <c r="G109" s="14" t="n"/>
+      <c r="H109" s="14" t="n"/>
+      <c r="I109" s="14" t="n"/>
+      <c r="J109" s="14" t="n"/>
+      <c r="K109" s="14" t="n"/>
+      <c r="L109" s="14" t="n"/>
+      <c r="M109" s="14" t="n"/>
+      <c r="N109" s="14" t="n"/>
+      <c r="O109" s="14" t="n"/>
+      <c r="P109" s="14" t="n"/>
+      <c r="Q109" s="14" t="n"/>
+      <c r="R109" s="14" t="n"/>
+      <c r="S109" s="14" t="n"/>
+      <c r="T109" s="14" t="n"/>
+      <c r="U109" s="14" t="n"/>
+      <c r="V109" s="14" t="n"/>
+      <c r="W109" s="14" t="n"/>
+      <c r="X109" s="14" t="n"/>
+      <c r="Y109" s="14" t="n"/>
+      <c r="Z109" s="14" t="n"/>
+      <c r="AA109" s="14" t="n"/>
+      <c r="AB109" s="14" t="n"/>
+      <c r="AC109" s="14" t="n"/>
+      <c r="AD109" s="14" t="n"/>
+      <c r="AE109" s="14" t="n"/>
+      <c r="AF109" s="14" t="n"/>
+      <c r="AG109" s="14" t="n"/>
+      <c r="AH109" s="14" t="n"/>
+      <c r="AI109" s="14" t="n"/>
+      <c r="AJ109" s="14" t="n"/>
+      <c r="AK109" s="14" t="n"/>
+      <c r="AL109" s="14" t="n"/>
+      <c r="AM109" s="14" t="n"/>
+      <c r="AN109" s="14" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A6:F6"/>
   <mergeCells count="3">
